--- a/StructureDefinition-onc-mental-capacity.xlsx
+++ b/StructureDefinition-onc-mental-capacity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-03T01:44:04+00:00</t>
+    <t>2026-01-03T21:32:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-mental-capacity.xlsx
+++ b/StructureDefinition-onc-mental-capacity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-03T21:32:36+00:00</t>
+    <t>2026-01-26T10:54:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-mental-capacity.xlsx
+++ b/StructureDefinition-onc-mental-capacity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-26T10:54:48+00:00</t>
+    <t>2026-01-26T11:35:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-mental-capacity.xlsx
+++ b/StructureDefinition-onc-mental-capacity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-26T11:35:16+00:00</t>
+    <t>2026-01-26T23:55:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-mental-capacity.xlsx
+++ b/StructureDefinition-onc-mental-capacity.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-26T23:55:12+00:00</t>
+    <t>2026-01-27T00:24:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-mental-capacity.xlsx
+++ b/StructureDefinition-onc-mental-capacity.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://fhir.clinyq.ai/StructureDefinition/onc-mental-capacity</t>
+    <t>https://opennursingcoreig.com/StructureDefinition/onc-mental-capacity</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-27T00:24:44+00:00</t>
+    <t>2026-01-27T01:09:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-mental-capacity.xlsx
+++ b/StructureDefinition-onc-mental-capacity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-27T01:09:05+00:00</t>
+    <t>2026-01-27T08:26:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-mental-capacity.xlsx
+++ b/StructureDefinition-onc-mental-capacity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-27T08:26:02+00:00</t>
+    <t>2026-01-27T09:30:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-mental-capacity.xlsx
+++ b/StructureDefinition-onc-mental-capacity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-27T09:30:37+00:00</t>
+    <t>2026-06-29T21:13:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-mental-capacity.xlsx
+++ b/StructureDefinition-onc-mental-capacity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T21:13:26+00:00</t>
+    <t>2026-07-04T08:39:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-mental-capacity.xlsx
+++ b/StructureDefinition-onc-mental-capacity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-04T08:39:09+00:00</t>
+    <t>2026-07-04T09:17:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-mental-capacity.xlsx
+++ b/StructureDefinition-onc-mental-capacity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-04T09:17:49+00:00</t>
+    <t>2026-07-09T21:51:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-mental-capacity.xlsx
+++ b/StructureDefinition-onc-mental-capacity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T21:51:52+00:00</t>
+    <t>2026-07-09T22:02:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-mental-capacity.xlsx
+++ b/StructureDefinition-onc-mental-capacity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T22:02:23+00:00</t>
+    <t>2026-07-09T22:05:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-mental-capacity.xlsx
+++ b/StructureDefinition-onc-mental-capacity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T22:05:12+00:00</t>
+    <t>2026-07-09T22:28:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-mental-capacity.xlsx
+++ b/StructureDefinition-onc-mental-capacity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T22:28:17+00:00</t>
+    <t>2026-07-10T11:01:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-mental-capacity.xlsx
+++ b/StructureDefinition-onc-mental-capacity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T11:01:35+00:00</t>
+    <t>2026-07-11T09:35:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-mental-capacity.xlsx
+++ b/StructureDefinition-onc-mental-capacity.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2032" uniqueCount="453">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2032" uniqueCount="452">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-11T09:35:24+00:00</t>
+    <t>2026-07-11T09:46:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -617,14 +617,6 @@
   </si>
   <si>
     <t>Used for filtering what observations are retrieved and displayed.</t>
-  </si>
-  <si>
-    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
-  &lt;coding&gt;
-    &lt;system value="http://terminology.hl7.org/CodeSystem/observation-category"/&gt;
-    &lt;code value="exam"/&gt;
-  &lt;/coding&gt;
-&lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
     <t>Codes for high level observation categories.</t>
@@ -3543,7 +3535,7 @@
         <v>18</v>
       </c>
       <c r="S15" t="s" s="2">
-        <v>193</v>
+        <v>18</v>
       </c>
       <c r="T15" t="s" s="2">
         <v>18</v>
@@ -3561,23 +3553,23 @@
         <v>114</v>
       </c>
       <c r="Y15" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="Z15" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="Z15" t="s" s="2">
+      <c r="AA15" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AB15" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="AA15" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>196</v>
       </c>
       <c r="AC15" s="2"/>
       <c r="AD15" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AF15" t="s" s="2">
         <v>187</v>
@@ -3604,10 +3596,10 @@
         <v>18</v>
       </c>
       <c r="AN15" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AO15" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="AO15" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>18</v>
@@ -3615,13 +3607,13 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B16" t="s" s="2">
         <v>187</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D16" t="s" s="2">
         <v>18</v>
@@ -3665,7 +3657,7 @@
         <v>18</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="T16" t="s" s="2">
         <v>18</v>
@@ -3683,10 +3675,10 @@
         <v>114</v>
       </c>
       <c r="Y16" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="Z16" t="s" s="2">
         <v>194</v>
-      </c>
-      <c r="Z16" t="s" s="2">
-        <v>195</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>18</v>
@@ -3728,10 +3720,10 @@
         <v>18</v>
       </c>
       <c r="AN16" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AO16" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="AO16" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="AP16" t="s" s="2">
         <v>18</v>
@@ -3739,14 +3731,14 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3768,16 +3760,16 @@
         <v>188</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="N17" t="s" s="2">
+      <c r="O17" t="s" s="2">
         <v>207</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>208</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>18</v>
@@ -3787,29 +3779,29 @@
         <v>18</v>
       </c>
       <c r="S17" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="T17" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="U17" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="V17" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="W17" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="X17" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="T17" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="U17" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="V17" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="W17" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="X17" t="s" s="2">
+      <c r="Y17" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="Y17" t="s" s="2">
+      <c r="Z17" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="Z17" t="s" s="2">
-        <v>212</v>
-      </c>
       <c r="AA17" t="s" s="2">
         <v>18</v>
       </c>
@@ -3826,7 +3818,7 @@
         <v>18</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>90</v>
@@ -3841,30 +3833,30 @@
         <v>102</v>
       </c>
       <c r="AK17" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="AL17" t="s" s="2">
         <v>213</v>
       </c>
-      <c r="AL17" t="s" s="2">
+      <c r="AM17" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="AM17" t="s" s="2">
+      <c r="AN17" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="AN17" t="s" s="2">
+      <c r="AO17" t="s" s="2">
         <v>216</v>
       </c>
-      <c r="AO17" t="s" s="2">
+      <c r="AP17" t="s" s="2">
         <v>217</v>
-      </c>
-      <c r="AP17" t="s" s="2">
-        <v>218</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3887,19 +3879,19 @@
         <v>91</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="L18" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="M18" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="N18" t="s" s="2">
+      <c r="O18" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>224</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>18</v>
@@ -3948,7 +3940,7 @@
         <v>18</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3963,19 +3955,19 @@
         <v>102</v>
       </c>
       <c r="AK18" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="AL18" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM18" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="AL18" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM18" t="s" s="2">
+      <c r="AN18" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="AN18" t="s" s="2">
+      <c r="AO18" t="s" s="2">
         <v>227</v>
-      </c>
-      <c r="AO18" t="s" s="2">
-        <v>228</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>18</v>
@@ -3983,10 +3975,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4009,16 +4001,16 @@
         <v>91</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>233</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -4068,7 +4060,7 @@
         <v>18</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -4089,13 +4081,13 @@
         <v>18</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>18</v>
@@ -4103,14 +4095,14 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -4129,19 +4121,19 @@
         <v>91</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>237</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="M20" t="s" s="2">
         <v>238</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>239</v>
       </c>
-      <c r="N20" t="s" s="2">
+      <c r="O20" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>241</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>18</v>
@@ -4190,7 +4182,7 @@
         <v>18</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -4205,19 +4197,19 @@
         <v>102</v>
       </c>
       <c r="AK20" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="AL20" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM20" t="s" s="2">
         <v>242</v>
       </c>
-      <c r="AL20" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM20" t="s" s="2">
+      <c r="AN20" t="s" s="2">
         <v>243</v>
       </c>
-      <c r="AN20" t="s" s="2">
+      <c r="AO20" t="s" s="2">
         <v>244</v>
-      </c>
-      <c r="AO20" t="s" s="2">
-        <v>245</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>18</v>
@@ -4225,14 +4217,14 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -4251,19 +4243,19 @@
         <v>91</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="M21" t="s" s="2">
         <v>249</v>
       </c>
-      <c r="M21" t="s" s="2">
+      <c r="N21" t="s" s="2">
         <v>250</v>
       </c>
-      <c r="N21" t="s" s="2">
+      <c r="O21" t="s" s="2">
         <v>251</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>252</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>18</v>
@@ -4312,7 +4304,7 @@
         <v>18</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -4327,19 +4319,19 @@
         <v>102</v>
       </c>
       <c r="AK21" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="AL21" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM21" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="AL21" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM21" t="s" s="2">
+      <c r="AN21" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="AN21" t="s" s="2">
+      <c r="AO21" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="AO21" t="s" s="2">
-        <v>256</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>18</v>
@@ -4347,10 +4339,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4373,16 +4365,16 @@
         <v>91</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="L22" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="L22" t="s" s="2">
+      <c r="M22" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="M22" t="s" s="2">
+      <c r="N22" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>261</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4432,7 +4424,7 @@
         <v>18</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -4453,13 +4445,13 @@
         <v>18</v>
       </c>
       <c r="AM22" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="AN22" t="s" s="2">
         <v>262</v>
       </c>
-      <c r="AN22" t="s" s="2">
+      <c r="AO22" t="s" s="2">
         <v>263</v>
-      </c>
-      <c r="AO22" t="s" s="2">
-        <v>264</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>18</v>
@@ -4467,10 +4459,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4493,17 +4485,17 @@
         <v>91</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="M23" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>18</v>
@@ -4552,7 +4544,7 @@
         <v>18</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4567,19 +4559,19 @@
         <v>102</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="AL23" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM23" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="AL23" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM23" t="s" s="2">
+      <c r="AN23" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="AN23" t="s" s="2">
+      <c r="AO23" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="AO23" t="s" s="2">
-        <v>273</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>18</v>
@@ -4587,10 +4579,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4616,16 +4608,16 @@
         <v>188</v>
       </c>
       <c r="L24" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="N24" t="s" s="2">
+      <c r="O24" t="s" s="2">
         <v>277</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>278</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>18</v>
@@ -4654,7 +4646,7 @@
       </c>
       <c r="Y24" s="2"/>
       <c r="Z24" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>18</v>
@@ -4672,7 +4664,7 @@
         <v>18</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4681,7 +4673,7 @@
         <v>90</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>102</v>
@@ -4690,27 +4682,27 @@
         <v>18</v>
       </c>
       <c r="AL24" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="AM24" t="s" s="2">
         <v>281</v>
       </c>
-      <c r="AM24" t="s" s="2">
+      <c r="AN24" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="AN24" t="s" s="2">
+      <c r="AO24" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP24" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="AO24" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP24" t="s" s="2">
-        <v>284</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4736,16 +4728,16 @@
         <v>188</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>287</v>
       </c>
-      <c r="N25" t="s" s="2">
+      <c r="O25" t="s" s="2">
         <v>288</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>289</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>18</v>
@@ -4770,14 +4762,14 @@
         <v>18</v>
       </c>
       <c r="X25" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="Y25" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="Y25" t="s" s="2">
+      <c r="Z25" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="Z25" t="s" s="2">
-        <v>292</v>
-      </c>
       <c r="AA25" t="s" s="2">
         <v>18</v>
       </c>
@@ -4794,7 +4786,7 @@
         <v>18</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4803,7 +4795,7 @@
         <v>90</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AJ25" t="s" s="2">
         <v>102</v>
@@ -4818,7 +4810,7 @@
         <v>133</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>18</v>
@@ -4829,14 +4821,14 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4858,16 +4850,16 @@
         <v>188</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="N26" t="s" s="2">
+      <c r="O26" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>300</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>18</v>
@@ -4892,14 +4884,14 @@
         <v>18</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="Y26" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="Z26" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="Z26" t="s" s="2">
-        <v>302</v>
-      </c>
       <c r="AA26" t="s" s="2">
         <v>18</v>
       </c>
@@ -4916,7 +4908,7 @@
         <v>18</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4934,27 +4926,27 @@
         <v>18</v>
       </c>
       <c r="AL26" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AM26" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="AM26" t="s" s="2">
+      <c r="AN26" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="AN26" t="s" s="2">
+      <c r="AO26" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP26" t="s" s="2">
         <v>305</v>
-      </c>
-      <c r="AO26" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP26" t="s" s="2">
-        <v>306</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4977,19 +4969,19 @@
         <v>18</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="L27" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="M27" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="N27" t="s" s="2">
+      <c r="O27" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>18</v>
@@ -5038,7 +5030,7 @@
         <v>18</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -5059,10 +5051,10 @@
         <v>18</v>
       </c>
       <c r="AM27" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="AN27" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>314</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>18</v>
@@ -5073,10 +5065,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5102,13 +5094,13 @@
         <v>188</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>316</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>317</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>318</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5134,14 +5126,14 @@
         <v>18</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="Y28" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="Z28" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="Z28" t="s" s="2">
-        <v>320</v>
-      </c>
       <c r="AA28" t="s" s="2">
         <v>18</v>
       </c>
@@ -5158,7 +5150,7 @@
         <v>18</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -5176,27 +5168,27 @@
         <v>18</v>
       </c>
       <c r="AL28" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="AM28" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="AM28" t="s" s="2">
+      <c r="AN28" t="s" s="2">
         <v>322</v>
       </c>
-      <c r="AN28" t="s" s="2">
+      <c r="AO28" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP28" t="s" s="2">
         <v>323</v>
-      </c>
-      <c r="AO28" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP28" t="s" s="2">
-        <v>324</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5222,16 +5214,16 @@
         <v>188</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="N29" t="s" s="2">
+      <c r="O29" t="s" s="2">
         <v>328</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>329</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>18</v>
@@ -5256,14 +5248,14 @@
         <v>18</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="Y29" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="Z29" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="Z29" t="s" s="2">
-        <v>331</v>
-      </c>
       <c r="AA29" t="s" s="2">
         <v>18</v>
       </c>
@@ -5280,7 +5272,7 @@
         <v>18</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -5301,10 +5293,10 @@
         <v>18</v>
       </c>
       <c r="AM29" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="AN29" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>333</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>18</v>
@@ -5315,10 +5307,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5341,16 +5333,16 @@
         <v>18</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="L30" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="L30" t="s" s="2">
+      <c r="M30" t="s" s="2">
         <v>336</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>337</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>338</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5400,7 +5392,7 @@
         <v>18</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -5418,27 +5410,27 @@
         <v>18</v>
       </c>
       <c r="AL30" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="AM30" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="AM30" t="s" s="2">
+      <c r="AN30" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="AN30" t="s" s="2">
+      <c r="AO30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP30" t="s" s="2">
         <v>341</v>
-      </c>
-      <c r="AO30" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP30" t="s" s="2">
-        <v>342</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5461,16 +5453,16 @@
         <v>18</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="L31" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="M31" t="s" s="2">
         <v>345</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>346</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>347</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5520,7 +5512,7 @@
         <v>18</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5538,27 +5530,27 @@
         <v>18</v>
       </c>
       <c r="AL31" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="AM31" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="AM31" t="s" s="2">
+      <c r="AN31" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="AN31" t="s" s="2">
+      <c r="AO31" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP31" t="s" s="2">
         <v>350</v>
-      </c>
-      <c r="AO31" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP31" t="s" s="2">
-        <v>351</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5581,19 +5573,19 @@
         <v>18</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="M32" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="N32" t="s" s="2">
+      <c r="O32" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>18</v>
@@ -5642,7 +5634,7 @@
         <v>18</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5654,19 +5646,19 @@
         <v>18</v>
       </c>
       <c r="AJ32" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="AK32" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AL32" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM32" t="s" s="2">
         <v>358</v>
       </c>
-      <c r="AK32" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AL32" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM32" t="s" s="2">
+      <c r="AN32" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="AN32" t="s" s="2">
-        <v>360</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>18</v>
@@ -5677,10 +5669,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5703,13 +5695,13 @@
         <v>18</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="L33" t="s" s="2">
         <v>362</v>
       </c>
-      <c r="L33" t="s" s="2">
+      <c r="M33" t="s" s="2">
         <v>363</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>364</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5760,7 +5752,7 @@
         <v>18</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5784,7 +5776,7 @@
         <v>18</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>18</v>
@@ -5795,10 +5787,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5827,7 +5819,7 @@
         <v>137</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="N34" t="s" s="2">
         <v>139</v>
@@ -5880,7 +5872,7 @@
         <v>18</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5904,7 +5896,7 @@
         <v>18</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>18</v>
@@ -5915,14 +5907,14 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -5944,10 +5936,10 @@
         <v>136</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>372</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>373</v>
       </c>
       <c r="N35" t="s" s="2">
         <v>139</v>
@@ -6002,7 +5994,7 @@
         <v>18</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -6037,10 +6029,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6063,13 +6055,13 @@
         <v>18</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="L36" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="L36" t="s" s="2">
+      <c r="M36" t="s" s="2">
         <v>377</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>378</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6120,7 +6112,7 @@
         <v>18</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -6129,7 +6121,7 @@
         <v>90</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>102</v>
@@ -6141,10 +6133,10 @@
         <v>18</v>
       </c>
       <c r="AM36" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="AN36" t="s" s="2">
         <v>380</v>
-      </c>
-      <c r="AN36" t="s" s="2">
-        <v>381</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>18</v>
@@ -6155,10 +6147,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6181,13 +6173,13 @@
         <v>18</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>383</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>384</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6238,7 +6230,7 @@
         <v>18</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -6247,7 +6239,7 @@
         <v>90</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>102</v>
@@ -6259,10 +6251,10 @@
         <v>18</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>18</v>
@@ -6273,10 +6265,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6302,16 +6294,16 @@
         <v>188</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>388</v>
       </c>
-      <c r="N38" t="s" s="2">
+      <c r="O38" t="s" s="2">
         <v>389</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>390</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>18</v>
@@ -6339,11 +6331,11 @@
         <v>114</v>
       </c>
       <c r="Y38" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="Z38" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="Z38" t="s" s="2">
-        <v>392</v>
-      </c>
       <c r="AA38" t="s" s="2">
         <v>18</v>
       </c>
@@ -6360,7 +6352,7 @@
         <v>18</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6378,13 +6370,13 @@
         <v>18</v>
       </c>
       <c r="AL38" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="AM38" t="s" s="2">
         <v>393</v>
       </c>
-      <c r="AM38" t="s" s="2">
-        <v>394</v>
-      </c>
       <c r="AN38" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>18</v>
@@ -6395,10 +6387,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6424,16 +6416,16 @@
         <v>188</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="N39" t="s" s="2">
+      <c r="O39" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>399</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>18</v>
@@ -6458,14 +6450,14 @@
         <v>18</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="Y39" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="Z39" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="Z39" t="s" s="2">
-        <v>401</v>
-      </c>
       <c r="AA39" t="s" s="2">
         <v>18</v>
       </c>
@@ -6482,7 +6474,7 @@
         <v>18</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6500,13 +6492,13 @@
         <v>18</v>
       </c>
       <c r="AL39" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="AM39" t="s" s="2">
         <v>393</v>
       </c>
-      <c r="AM39" t="s" s="2">
-        <v>394</v>
-      </c>
       <c r="AN39" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>18</v>
@@ -6517,10 +6509,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6543,17 +6535,17 @@
         <v>18</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="L40" t="s" s="2">
         <v>403</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="M40" t="s" s="2">
         <v>404</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>405</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>18</v>
@@ -6602,7 +6594,7 @@
         <v>18</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6626,7 +6618,7 @@
         <v>18</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>18</v>
@@ -6637,10 +6629,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6663,13 +6655,13 @@
         <v>18</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>409</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>410</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6720,7 +6712,7 @@
         <v>18</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6741,10 +6733,10 @@
         <v>18</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>18</v>
@@ -6755,10 +6747,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6781,16 +6773,16 @@
         <v>91</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="M42" t="s" s="2">
         <v>414</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>415</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>416</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6840,7 +6832,7 @@
         <v>18</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6861,10 +6853,10 @@
         <v>18</v>
       </c>
       <c r="AM42" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="AN42" t="s" s="2">
         <v>417</v>
-      </c>
-      <c r="AN42" t="s" s="2">
-        <v>418</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>18</v>
@@ -6875,10 +6867,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6901,16 +6893,16 @@
         <v>91</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="L43" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="M43" t="s" s="2">
         <v>421</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>422</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>423</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6960,7 +6952,7 @@
         <v>18</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6981,10 +6973,10 @@
         <v>18</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>18</v>
@@ -6995,10 +6987,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7021,19 +7013,19 @@
         <v>91</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="N44" t="s" s="2">
         <v>427</v>
       </c>
-      <c r="N44" t="s" s="2">
+      <c r="O44" t="s" s="2">
         <v>428</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>429</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>18</v>
@@ -7082,7 +7074,7 @@
         <v>18</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -7103,10 +7095,10 @@
         <v>18</v>
       </c>
       <c r="AM44" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AN44" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="AN44" t="s" s="2">
-        <v>431</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>18</v>
@@ -7117,10 +7109,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7143,13 +7135,13 @@
         <v>18</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="L45" t="s" s="2">
         <v>362</v>
       </c>
-      <c r="L45" t="s" s="2">
+      <c r="M45" t="s" s="2">
         <v>363</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>364</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7200,7 +7192,7 @@
         <v>18</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -7224,7 +7216,7 @@
         <v>18</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>18</v>
@@ -7235,10 +7227,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7267,7 +7259,7 @@
         <v>137</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="N46" t="s" s="2">
         <v>139</v>
@@ -7320,7 +7312,7 @@
         <v>18</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7344,7 +7336,7 @@
         <v>18</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>18</v>
@@ -7355,14 +7347,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7384,10 +7376,10 @@
         <v>136</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>372</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>373</v>
       </c>
       <c r="N47" t="s" s="2">
         <v>139</v>
@@ -7442,7 +7434,7 @@
         <v>18</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7477,10 +7469,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7506,16 +7498,16 @@
         <v>188</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="N48" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="N48" t="s" s="2">
-        <v>438</v>
-      </c>
       <c r="O48" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>18</v>
@@ -7540,14 +7532,14 @@
         <v>18</v>
       </c>
       <c r="X48" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="Y48" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="Y48" t="s" s="2">
+      <c r="Z48" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="Z48" t="s" s="2">
-        <v>212</v>
-      </c>
       <c r="AA48" t="s" s="2">
         <v>18</v>
       </c>
@@ -7564,7 +7556,7 @@
         <v>18</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>90</v>
@@ -7582,16 +7574,16 @@
         <v>18</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AM48" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AN48" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="AN48" t="s" s="2">
+      <c r="AO48" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="AO48" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>18</v>
@@ -7599,10 +7591,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7625,19 +7617,19 @@
         <v>91</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="L49" t="s" s="2">
         <v>441</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="M49" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="N49" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="M49" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>443</v>
-      </c>
       <c r="O49" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>18</v>
@@ -7686,7 +7678,7 @@
         <v>18</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7704,27 +7696,27 @@
         <v>18</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="AM49" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="AN49" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="AN49" t="s" s="2">
+      <c r="AO49" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP49" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="AO49" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP49" t="s" s="2">
-        <v>284</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7750,16 +7742,16 @@
         <v>188</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>447</v>
       </c>
-      <c r="N50" t="s" s="2">
-        <v>448</v>
-      </c>
       <c r="O50" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>18</v>
@@ -7784,14 +7776,14 @@
         <v>18</v>
       </c>
       <c r="X50" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="Y50" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="Y50" t="s" s="2">
+      <c r="Z50" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="Z50" t="s" s="2">
-        <v>292</v>
-      </c>
       <c r="AA50" t="s" s="2">
         <v>18</v>
       </c>
@@ -7808,7 +7800,7 @@
         <v>18</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7817,7 +7809,7 @@
         <v>90</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>102</v>
@@ -7832,7 +7824,7 @@
         <v>133</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>18</v>
@@ -7843,14 +7835,14 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -7872,16 +7864,16 @@
         <v>188</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="M51" t="s" s="2">
+      <c r="N51" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="N51" t="s" s="2">
+      <c r="O51" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>300</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>18</v>
@@ -7906,14 +7898,14 @@
         <v>18</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="Y51" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="Z51" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="Z51" t="s" s="2">
-        <v>302</v>
-      </c>
       <c r="AA51" t="s" s="2">
         <v>18</v>
       </c>
@@ -7930,7 +7922,7 @@
         <v>18</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7948,27 +7940,27 @@
         <v>18</v>
       </c>
       <c r="AL51" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AM51" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="AM51" t="s" s="2">
+      <c r="AN51" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="AN51" t="s" s="2">
+      <c r="AO51" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP51" t="s" s="2">
         <v>305</v>
-      </c>
-      <c r="AO51" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP51" t="s" s="2">
-        <v>306</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7994,16 +7986,16 @@
         <v>80</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="M52" t="s" s="2">
-        <v>452</v>
-      </c>
       <c r="N52" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="O52" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>18</v>
@@ -8052,7 +8044,7 @@
         <v>18</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -8073,10 +8065,10 @@
         <v>18</v>
       </c>
       <c r="AM52" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="AN52" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>360</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>18</v>

--- a/StructureDefinition-onc-mental-capacity.xlsx
+++ b/StructureDefinition-onc-mental-capacity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-11T09:46:48+00:00</t>
+    <t>2026-07-11T14:02:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-mental-capacity.xlsx
+++ b/StructureDefinition-onc-mental-capacity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-11T14:02:42+00:00</t>
+    <t>2026-07-11T14:17:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-mental-capacity.xlsx
+++ b/StructureDefinition-onc-mental-capacity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-11T14:17:07+00:00</t>
+    <t>2026-07-11T14:32:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-mental-capacity.xlsx
+++ b/StructureDefinition-onc-mental-capacity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-11T14:32:04+00:00</t>
+    <t>2026-07-11T14:47:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-mental-capacity.xlsx
+++ b/StructureDefinition-onc-mental-capacity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-11T14:47:20+00:00</t>
+    <t>2026-07-11T18:02:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
